--- a/Graph/Others/WT-T2-TiTa_inward_filtered.xlsx
+++ b/Graph/Others/WT-T2-TiTa_inward_filtered.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agrawal-admin\Desktop\Landing\Graph\Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998E33A5-69F2-4B44-8B22-96B5B7E40DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B8835D-FD95-4F4B-B1CE-EE622001FC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="25">
   <si>
     <t>Fly#</t>
   </si>
@@ -115,7 +115,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,12 +154,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor rgb="FFFF6666"/>
       </patternFill>
@@ -180,6 +174,18 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -210,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -225,6 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,19 +674,19 @@
       <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>65</v>
       </c>
       <c r="D3" s="3">
         <v>63</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>24</v>
+      <c r="E3" s="11">
+        <v>46</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -706,10 +713,10 @@
       <c r="O3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="8" t="s">
+      <c r="P3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="7" t="s">
         <v>24</v>
       </c>
       <c r="R3" s="2" t="s">
@@ -747,7 +754,7 @@
       <c r="G4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="I4" s="4" t="s">
@@ -762,14 +769,14 @@
       <c r="L4" s="3">
         <v>32</v>
       </c>
-      <c r="M4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>24</v>
+      <c r="M4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="11">
+        <v>53</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>22</v>
@@ -780,7 +787,7 @@
       <c r="R4" s="3">
         <v>29</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="T4" s="4" t="s">
@@ -859,8 +866,8 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
+      <c r="B6" s="3">
+        <v>41</v>
       </c>
       <c r="C6" s="3">
         <v>30</v>
@@ -913,10 +920,10 @@
       <c r="S6" s="3">
         <v>26</v>
       </c>
-      <c r="T6" s="10">
+      <c r="T6" s="9">
         <v>72</v>
       </c>
-      <c r="U6" s="10">
+      <c r="U6" s="9">
         <v>27</v>
       </c>
     </row>
@@ -924,8 +931,8 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>23</v>
@@ -954,7 +961,7 @@
       <c r="K7" s="3">
         <v>74</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="7" t="s">
         <v>24</v>
       </c>
       <c r="M7" s="3">
@@ -975,7 +982,7 @@
       <c r="R7" s="3">
         <v>101</v>
       </c>
-      <c r="S7" s="10">
+      <c r="S7" s="9">
         <v>135</v>
       </c>
       <c r="T7" s="3">
@@ -1019,7 +1026,7 @@
       <c r="K8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M8" s="2" t="s">
@@ -1034,7 +1041,7 @@
       <c r="P8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="10" t="s">
         <v>21</v>
       </c>
       <c r="R8" s="2" t="s">
@@ -1057,7 +1064,7 @@
       <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="3">
         <v>91</v>
       </c>
       <c r="D9" s="3">
@@ -1190,22 +1197,22 @@
       <c r="C11" s="3">
         <v>33</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>24</v>
+      <c r="D11" s="11">
+        <v>95</v>
+      </c>
+      <c r="E11" s="11">
+        <v>74</v>
+      </c>
+      <c r="F11" s="11">
+        <v>102</v>
       </c>
       <c r="G11" s="3">
         <v>73</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>151</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>24</v>
       </c>
       <c r="J11" s="3">
@@ -1217,7 +1224,7 @@
       <c r="L11" s="3">
         <v>33</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="M11" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N11" s="3">
@@ -1229,7 +1236,7 @@
       <c r="P11" s="3">
         <v>54</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="9">
         <v>35</v>
       </c>
       <c r="R11" s="3">
@@ -1264,7 +1271,7 @@
       <c r="F12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -1288,13 +1295,13 @@
       <c r="N12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Q12" s="10" t="s">
+      <c r="Q12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="R12" s="2" t="s">
@@ -1303,7 +1310,7 @@
       <c r="S12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T12" s="10" t="s">
+      <c r="T12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="U12" s="2" t="s">
@@ -1347,8 +1354,8 @@
       <c r="L13" s="3">
         <v>237</v>
       </c>
-      <c r="M13" s="8" t="s">
-        <v>24</v>
+      <c r="M13" s="12">
+        <v>383</v>
       </c>
       <c r="N13" s="3">
         <v>26</v>
@@ -1400,7 +1407,7 @@
       <c r="H14" s="3">
         <v>96</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>66</v>
       </c>
       <c r="J14" s="3">
@@ -1465,7 +1472,7 @@
       <c r="H15" s="3">
         <v>30</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <v>160</v>
       </c>
       <c r="J15" s="3">
@@ -1527,19 +1534,19 @@
       <c r="G16" s="3">
         <v>78</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="11">
+      <c r="H16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="10">
         <v>-1</v>
       </c>
       <c r="J16" s="3">
         <v>152</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="8">
         <v>68</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="7" t="s">
         <v>24</v>
       </c>
       <c r="M16" s="3">
@@ -1554,10 +1561,10 @@
       <c r="P16" s="3">
         <v>103</v>
       </c>
-      <c r="Q16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R16" s="8" t="s">
+      <c r="Q16" s="11">
+        <v>196</v>
+      </c>
+      <c r="R16" s="7" t="s">
         <v>24</v>
       </c>
       <c r="S16" s="3">
@@ -1566,7 +1573,7 @@
       <c r="T16" s="3">
         <v>69</v>
       </c>
-      <c r="U16" s="8" t="s">
+      <c r="U16" s="7" t="s">
         <v>24</v>
       </c>
     </row>
